--- a/output/pdf_financials_xlsx/NICO.xlsx
+++ b/output/pdf_financials_xlsx/NICO.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>2.515641</v>
+        <v>3.757277</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>2.901757</v>
+        <v>4.143393</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.901757</v>
+        <v>4.143393</v>
       </c>
     </row>
     <row r="93">
@@ -3067,7 +3067,11 @@
           <t>Warrant reserve (note 9)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>1.241636</v>
       </c>

--- a/output/pdf_financials_xlsx/NICO.xlsx
+++ b/output/pdf_financials_xlsx/NICO.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000745</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023293</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000709</v>
       </c>
     </row>
     <row r="13">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.023043</v>
+        <v>-2.022298</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.044711</v>
+        <v>-2.021418</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.586037</v>
+        <v>-1.585328</v>
       </c>
     </row>
     <row r="28">
@@ -899,13 +899,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.023043</v>
+        <v>-2.022298</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.044711</v>
+        <v>-2.021418</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.586037</v>
+        <v>-1.585328</v>
       </c>
     </row>
     <row r="30">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
